--- a/sports_forms/015_youth_sports_video_story_consent_form--sports_forms.xlsx
+++ b/sports_forms/015_youth_sports_video_story_consent_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent',_'label':_"parent's_email"}</t>
+          <t>parent's_email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'parent', 'label': "Parent's Email"}</t>
+          <t>Parent's Email</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'coach',_'label':_'coach/assistant_coach'}</t>
+          <t>coach/assistant_coach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'coach', 'label': 'Coach/Assistant Coach'}</t>
+          <t>Coach/Assistant Coach</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'organization',_'label':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'organization', 'label': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent',_'label':_"parent's_email"}</t>
+          <t>parent's_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'parent', 'label': "Parent's Email"}</t>
+          <t>Parent's Email</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'coach',_'label':_'coach/assistant_coach'}</t>
+          <t>coach/assistant_coach</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'coach', 'label': 'Coach/Assistant Coach'}</t>
+          <t>Coach/Assistant Coach</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'organization',_'label':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'organization', 'label': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'analytics',_'label':_'analytics'}</t>
+          <t>analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'analytics', 'label': 'Analytics'}</t>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non_analytics',_'label':_'non-analytics'}</t>
+          <t>non-analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'non_analytics', 'label': 'Non-Analytics'}</t>
+          <t>Non-Analytics</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'staff',_'label':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'staff', 'label': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facebook',_'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'facebook', 'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'instagram',_'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'instagram', 'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'twitter',_'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'twitter', 'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent',_'label':_'parent/guardian'}</t>
+          <t>parent/guardian</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'parent', 'label': 'Parent/Guardian'}</t>
+          <t>Parent/Guardian</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'coach',_'label':_'coach/assistant_coach'}</t>
+          <t>coach/assistant_coach</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'coach', 'label': 'Coach/Assistant Coach'}</t>
+          <t>Coach/Assistant Coach</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'staff',_'label':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'staff', 'label': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
